--- a/dados.xlsx
+++ b/dados.xlsx
@@ -425,53 +425,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LLPP/GERENTE DE ARÉA:</t>
+          <t>OPERAÇÃO</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Meta/Dia</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Real:</t>
+          <t xml:space="preserve">ALTA PÓS PURO(RECEITA) </t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTA PÓS PURO (FÍSICO) </t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SHOPPING IGUATEMI</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>350</v>
-      </c>
-      <c r="C2" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SHOPPING LAPA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>SHOPPING IGUATEMI1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13/05/25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
     </row>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +453,41 @@
           <t xml:space="preserve">ALTA PÓS PURO (FÍSICO) </t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MIGRA PRÉ/CTRL PURO(RECEITA)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MIGRA PRÉ/CTRL PURO(FÍSICO)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ALTA CONTROLE (RECEITA)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ALTA CONTROLE (FÍSICO)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MIGRA CTRL PRÉ (RECEITA)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MIGRA CTRL PRÉ (FÍSICO)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>PORTABILIDADE</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -461,14 +500,68 @@
           <t>13/05/25</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>123</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SHOPPING IGUATEMI1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45841</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>23</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
     </row>
